--- a/excel/Loanch.xlsx
+++ b/excel/Loanch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Loanch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57428380-D981-4CCC-94C3-9458B318CA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D57DEA6-A7C9-4BC2-A6D6-C4CE53F612F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z3" s="31">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.12009962201118468</v>
+        <v>0.11481881737709046</v>
       </c>
       <c r="AA3" s="29">
         <f>SUM(O3:O100)</f>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="K9" s="19">
         <f ca="1">'6836f159...155f27704bef'!B12</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L9" s="19" t="str">
         <f ca="1">'6836f159...155f27704bef'!P3</f>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="K11" s="19">
         <f ca="1">'45b52ba0...0700af8e066e'!B12</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L11" s="19" t="str">
         <f ca="1">'45b52ba0...0700af8e066e'!P3</f>
@@ -6693,7 +6693,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="15">
         <f ca="1">TODAY()</f>
-        <v>46231</v>
+        <v>46235</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="6"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="6"/>

--- a/excel/Loanch.xlsx
+++ b/excel/Loanch.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Loanch\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evald\OneDrive\Dokumentai\portfolio-analytics\portfolio-dashboard-clean\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D57DEA6-A7C9-4BC2-A6D6-C4CE53F612F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0080911B-2B33-45E1-829A-BF243F98D892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z3" s="31">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.11481881737709046</v>
+        <v>0.10448089241981506</v>
       </c>
       <c r="AA3" s="29">
         <f>SUM(O3:O100)</f>
@@ -2178,11 +2178,11 @@
       </c>
       <c r="K9" s="19">
         <f ca="1">'6836f159...155f27704bef'!B12</f>
-        <v>3</v>
-      </c>
-      <c r="L9" s="19" t="str">
+        <v>-6</v>
+      </c>
+      <c r="L9" s="19">
         <f ca="1">'6836f159...155f27704bef'!P3</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="M9" s="3">
         <f>'6836f159...155f27704bef'!K3</f>
@@ -2199,7 +2199,7 @@
       <c r="P9" s="10"/>
       <c r="AC9" s="3" t="str">
         <f ca="1">'6836f159...155f27704bef'!Z3</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="K11" s="19">
         <f ca="1">'45b52ba0...0700af8e066e'!B12</f>
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="L11" s="19" t="str">
         <f ca="1">'45b52ba0...0700af8e066e'!P3</f>
@@ -6693,7 +6693,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="15">
         <f ca="1">TODAY()</f>
-        <v>46235</v>
+        <v>46244</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6824,7 +6824,7 @@
         <v>36</v>
       </c>
       <c r="D3" s="11">
-        <v>46238</v>
+        <v>46261</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="19" t="str">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="6"/>
@@ -9416,9 +9416,9 @@
         <f>IF(B16=K3,MAX(E:E),"")</f>
         <v/>
       </c>
-      <c r="P3" s="2" t="str">
+      <c r="P3" s="2">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="Q3" s="2" t="str">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="6"/>

--- a/excel/Loanch.xlsx
+++ b/excel/Loanch.xlsx
@@ -5,25 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evald\OneDrive\Dokumentai\portfolio-analytics\portfolio-dashboard-clean\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Loanch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0080911B-2B33-45E1-829A-BF243F98D892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC66B2A3-2C28-4D74-80EB-1EE7C65DD0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="15" r:id="rId2"/>
-    <sheet name="45b52ba0...0700af8e066e" sheetId="31" r:id="rId3"/>
-    <sheet name="4db6f5a8...8acf4fb9b90a" sheetId="30" r:id="rId4"/>
-    <sheet name="6836f159...155f27704bef" sheetId="29" r:id="rId5"/>
-    <sheet name="bab06fd6...b5601686ad35" sheetId="28" r:id="rId6"/>
-    <sheet name="6503e9b8...38a61e9781c1" sheetId="27" r:id="rId7"/>
-    <sheet name="edcaf7c8...13263f96f7ec" sheetId="26" r:id="rId8"/>
-    <sheet name="34060e5d...9d09fabf263e" sheetId="25" r:id="rId9"/>
-    <sheet name="8572f54e...85fb68b6201e" sheetId="24" r:id="rId10"/>
-    <sheet name="6a67a901...550919b8d681" sheetId="14" r:id="rId11"/>
+    <sheet name="90203940...099922b10dbd" sheetId="32" r:id="rId3"/>
+    <sheet name="45b52ba0...0700af8e066e" sheetId="31" r:id="rId4"/>
+    <sheet name="4db6f5a8...8acf4fb9b90a" sheetId="30" r:id="rId5"/>
+    <sheet name="6836f159...155f27704bef" sheetId="29" r:id="rId6"/>
+    <sheet name="bab06fd6...b5601686ad35" sheetId="28" r:id="rId7"/>
+    <sheet name="6503e9b8...38a61e9781c1" sheetId="27" r:id="rId8"/>
+    <sheet name="edcaf7c8...13263f96f7ec" sheetId="26" r:id="rId9"/>
+    <sheet name="34060e5d...9d09fabf263e" sheetId="25" r:id="rId10"/>
+    <sheet name="8572f54e...85fb68b6201e" sheetId="24" r:id="rId11"/>
+    <sheet name="6a67a901...550919b8d681" sheetId="14" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="55">
   <si>
     <t>Paskola</t>
   </si>
@@ -208,6 +209,9 @@
   </si>
   <si>
     <t>45b52ba0...0700af8e066e</t>
+  </si>
+  <si>
+    <t>90203940...099922b10dbd</t>
   </si>
 </sst>
 </file>
@@ -371,7 +375,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -450,6 +454,12 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -482,7 +492,35 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="44">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -797,7 +835,63 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E270EAFC-C8EA-4366-981D-24AE62039ECD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AE201A7-E401-4298-8793-43702E58B25B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13114388-3521-4DB4-98A1-45633E6AB57C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -853,7 +947,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2A7DB54-D366-4D84-B86A-9127CFF165AF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E270EAFC-C8EA-4366-981D-24AE62039ECD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -909,7 +1003,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6699D495-B184-490D-A9BE-00D1D918D297}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2A7DB54-D366-4D84-B86A-9127CFF165AF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -965,7 +1059,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6093F4BF-7670-408C-9E02-CC8C7C81DD2D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6699D495-B184-490D-A9BE-00D1D918D297}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1021,7 +1115,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F94C725A-4ADE-42D1-9C31-B09433946415}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6093F4BF-7670-408C-9E02-CC8C7C81DD2D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1077,7 +1171,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFD5E720-E4DB-43B4-8450-81B1D8305FDB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F94C725A-4ADE-42D1-9C31-B09433946415}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1133,7 +1227,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BA58F80-4A4F-4820-9AC1-8CCD158423E9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFD5E720-E4DB-43B4-8450-81B1D8305FDB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1189,7 +1283,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F3E6BE7-2620-4CB3-8F4E-0C17BF712D36}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BA58F80-4A4F-4820-9AC1-8CCD158423E9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1245,7 +1339,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13114388-3521-4DB4-98A1-45633E6AB57C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F3E6BE7-2620-4CB3-8F4E-0C17BF712D36}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1560,43 +1654,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="32" t="s">
+      <c r="A1" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="37" t="s">
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="Q1" s="38" t="s">
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="Q1" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="38" t="s">
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="V1" s="40"/>
-      <c r="W1" s="32" t="s">
+      <c r="V1" s="42"/>
+      <c r="W1" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
       <c r="AA1" s="4" t="s">
         <v>25</v>
       </c>
@@ -1752,7 +1846,7 @@
       </c>
       <c r="R3" s="29">
         <f>SUM(H3:H100)-U3</f>
-        <v>20.580000000000013</v>
+        <v>20.700000000000003</v>
       </c>
       <c r="S3" s="30">
         <f>Pinigai!H2</f>
@@ -1764,27 +1858,27 @@
       </c>
       <c r="U3" s="29">
         <f>SUM(M3:M100)</f>
-        <v>70.64</v>
+        <v>80.98</v>
       </c>
       <c r="V3" s="29">
         <f>SUM(N3:N100)-AA3</f>
-        <v>0.57999999999999996</v>
+        <v>0.7</v>
       </c>
       <c r="W3" s="29">
         <f>Q3+V3+S3</f>
-        <v>20.58</v>
+        <v>20.7</v>
       </c>
       <c r="X3" s="29">
         <f>W3-Q3</f>
-        <v>0.57999999999999829</v>
+        <v>0.69999999999999929</v>
       </c>
       <c r="Y3" s="31">
         <f>(W3-Q3)/Q3</f>
-        <v>2.8999999999999915E-2</v>
+        <v>3.4999999999999962E-2</v>
       </c>
       <c r="Z3" s="31">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.10448089241981506</v>
+        <v>0.10478962063789368</v>
       </c>
       <c r="AA3" s="29">
         <f>SUM(O3:O100)</f>
@@ -2178,11 +2272,11 @@
       </c>
       <c r="K9" s="19">
         <f ca="1">'6836f159...155f27704bef'!B12</f>
-        <v>-6</v>
+        <v>-27</v>
       </c>
       <c r="L9" s="19">
         <f ca="1">'6836f159...155f27704bef'!P3</f>
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="M9" s="3">
         <f>'6836f159...155f27704bef'!K3</f>
@@ -2304,13 +2398,13 @@
         <f>'45b52ba0...0700af8e066e'!B11</f>
         <v>46261</v>
       </c>
-      <c r="J11" s="6" t="str">
+      <c r="J11" s="6">
         <f>'45b52ba0...0700af8e066e'!O3</f>
-        <v/>
-      </c>
-      <c r="K11" s="19">
+        <v>46261</v>
+      </c>
+      <c r="K11" s="19" t="str">
         <f ca="1">'45b52ba0...0700af8e066e'!B12</f>
-        <v>17</v>
+        <v/>
       </c>
       <c r="L11" s="19" t="str">
         <f ca="1">'45b52ba0...0700af8e066e'!P3</f>
@@ -2318,11 +2412,11 @@
       </c>
       <c r="M11" s="3">
         <f>'45b52ba0...0700af8e066e'!K3</f>
-        <v>0</v>
+        <v>10.34</v>
       </c>
       <c r="N11" s="3">
         <f>'45b52ba0...0700af8e066e'!L3</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="O11" s="3">
         <f>'45b52ba0...0700af8e066e'!M3</f>
@@ -2335,22 +2429,70 @@
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="3"/>
-      <c r="AC12" s="1"/>
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6">
+        <f>'90203940...099922b10dbd'!B9</f>
+        <v>46261</v>
+      </c>
+      <c r="C12" s="26" t="str">
+        <f>'90203940...099922b10dbd'!B1</f>
+        <v>90203940...099922b10dbd</v>
+      </c>
+      <c r="D12" s="2" t="str">
+        <f>'90203940...099922b10dbd'!B2</f>
+        <v>Malaysia</v>
+      </c>
+      <c r="E12" s="2" t="str">
+        <f>'90203940...099922b10dbd'!B3</f>
+        <v>Tambadana</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <f>'90203940...099922b10dbd'!B8</f>
+        <v>0 m. 0 mėn. 30 d.</v>
+      </c>
+      <c r="G12" s="7">
+        <f>'90203940...099922b10dbd'!B15</f>
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="H12" s="3">
+        <f>'90203940...099922b10dbd'!B16</f>
+        <v>10.46</v>
+      </c>
+      <c r="I12" s="6">
+        <f>'90203940...099922b10dbd'!B11</f>
+        <v>46291</v>
+      </c>
+      <c r="J12" s="6" t="str">
+        <f>'90203940...099922b10dbd'!O3</f>
+        <v/>
+      </c>
+      <c r="K12" s="19">
+        <f ca="1">'90203940...099922b10dbd'!B12</f>
+        <v>26</v>
+      </c>
+      <c r="L12" s="19" t="str">
+        <f ca="1">'90203940...099922b10dbd'!P3</f>
+        <v/>
+      </c>
+      <c r="M12" s="3">
+        <f>'90203940...099922b10dbd'!K3</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <f>'90203940...099922b10dbd'!L3</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="3">
+        <f>'90203940...099922b10dbd'!M3</f>
+        <v>0</v>
+      </c>
+      <c r="P12" s="10"/>
+      <c r="AC12" s="3" t="str">
+        <f ca="1">'90203940...099922b10dbd'!Z3</f>
+        <v/>
+      </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
@@ -2632,20 +2774,20 @@
     <mergeCell ref="U1:V1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:O27">
-    <cfRule type="expression" dxfId="39" priority="15">
+    <cfRule type="expression" dxfId="43" priority="15">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="16">
+    <cfRule type="expression" dxfId="42" priority="16">
       <formula>AND($M3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC3:AC27">
-    <cfRule type="expression" dxfId="37" priority="2">
+    <cfRule type="expression" dxfId="41" priority="2">
       <formula>AND($M3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC5:AC11">
-    <cfRule type="expression" dxfId="36" priority="1">
+  <conditionalFormatting sqref="AC5:AC12">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>$AC5="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2659,6 +2801,7 @@
     <hyperlink ref="C9" location="'6836f159...155f27704bef'!A1" display="'6836f159...155f27704bef'!A1" xr:uid="{6FBE713B-C5C1-4487-AEB0-76FB8384D359}"/>
     <hyperlink ref="C10" location="'4db6f5a8...8acf4fb9b90a'!A1" display="'4db6f5a8...8acf4fb9b90a'!A1" xr:uid="{51C54BD2-6758-450A-BD35-5AEE8C98C71A}"/>
     <hyperlink ref="C11" location="'45b52ba0...0700af8e066e'!A1" display="'45b52ba0...0700af8e066e'!A1" xr:uid="{99FD08BF-C515-4DD4-9F3D-763A30898E51}"/>
+    <hyperlink ref="C12" location="'45b52ba0...0700af8e066e'!A1" display="'45b52ba0...0700af8e066e'!A1" xr:uid="{C5788568-CC7C-49A1-B48C-5CA88B7536B0}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="50" orientation="landscape" r:id="rId1"/>
@@ -2666,6 +2809,1292 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D73BEB5-FF23-4AB2-910E-BFC1E1552858}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46181</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46177</v>
+      </c>
+      <c r="F3" s="19">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v>-4</v>
+      </c>
+      <c r="G3" s="3">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>10.029999999999999</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0.1</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v>0.1435224711894989</v>
+      </c>
+      <c r="O3" s="6">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v>46177</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v>-4</v>
+      </c>
+      <c r="T3" s="13"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46150</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-10.029999999999999</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="19" t="str">
+        <f>IF(E4&gt;0,E4-D4,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="10"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46177</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>10.129999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="19" t="str">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="10"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="10"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="14"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 1 mėn. 0 d.</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="10"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46150</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="14"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46150</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="14"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46181</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="14"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="19" t="str">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="14"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="18"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="14"/>
+      <c r="N13" s="13"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="18"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="14"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="11"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="14"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="11"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="14"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="11"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="14"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="11"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="14"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B21" s="23"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="14"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="11"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="14"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="11"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="14"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="11"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="14"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="11"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="14"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="11"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="14"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="11"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="14"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="11"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="14"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="11"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="14"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="11"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="14"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="11"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="14"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="11"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="14"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="11"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="14"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="11"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="14"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="11"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="14"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="11"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="14"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="11"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="14"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="11"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="14"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="11"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="14"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="11"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="14"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="11"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="14"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="11"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="14"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="11"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="14"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="11"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="14"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="11"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="14"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="11"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="14"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="11"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="14"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="11"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="14"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="11"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="14"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="11"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="14"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="11"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="14"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="11"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="10"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="22"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>10.029999999999999</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0.1</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="13" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="12" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{583E60DD-D268-4B5D-B986-F933A571227C}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -2695,29 +4124,29 @@
       <c r="B1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -3928,20 +5357,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="9" priority="5">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="8" priority="6">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3951,7 +5380,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -3981,29 +5410,29 @@
       <c r="B1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -5213,20 +6642,20 @@
     <mergeCell ref="X1:Z1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>$Z$3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>$B$16=$K$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>$Z$3="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6693,14 +8122,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="15">
         <f ca="1">TODAY()</f>
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="3">
         <f>Overview!W3</f>
-        <v>20.58</v>
+        <v>20.7</v>
       </c>
     </row>
   </sheetData>
@@ -6709,7 +8138,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D413F8-1679-4095-AA32-963FC106BE84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBD262D-AFFA-4485-9906-FB8E3EB69FC9}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6733,31 +8162,31 @@
         <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -6766,53 +8195,53 @@
       <c r="B2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="33" t="s">
         <v>29</v>
       </c>
       <c r="J2" s="10"/>
-      <c r="K2" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="12" t="s">
+      <c r="K2" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="P2" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="X2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Y2" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="Z2" s="33" t="s">
         <v>41</v>
       </c>
     </row>
@@ -6823,9 +8252,7 @@
       <c r="B3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="11">
-        <v>46261</v>
-      </c>
+      <c r="D3" s="11"/>
       <c r="E3" s="6"/>
       <c r="F3" s="19" t="str">
         <f>IF(E3&gt;0,E3-D3,"")</f>
@@ -6835,18 +8262,9 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="14"/>
-      <c r="K3" s="3">
-        <f>G53</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <f>H53</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <f>I53</f>
-        <v>0</v>
-      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
       <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
         <v/>
@@ -6866,11 +8284,11 @@
       <c r="T3" s="13"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>46231</v>
+        <v>46261</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-10.34</v>
+        <v>-10.46</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -7001,7 +8419,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>46231</v>
+        <v>46261</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="6"/>
@@ -7027,7 +8445,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="6">
-        <v>46231</v>
+        <v>46261</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="6"/>
@@ -7053,7 +8471,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="6">
-        <v>46261</v>
+        <v>46291</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="6"/>
@@ -7080,7 +8498,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="6"/>
@@ -7184,7 +8602,7 @@
         <v>40</v>
       </c>
       <c r="B16" s="3">
-        <v>10.34</v>
+        <v>10.46</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="6"/>
@@ -7946,6 +9364,2578 @@
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
         <v>0</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D413F8-1679-4095-AA32-963FC106BE84}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46261</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46261</v>
+      </c>
+      <c r="F3" s="19">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>10.34</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>10.34</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0.12</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v>0.15071808695793154</v>
+      </c>
+      <c r="O3" s="6">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v>46261</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v>0</v>
+      </c>
+      <c r="T3" s="13"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46231</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-10.34</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="19" t="str">
+        <f>IF(E4&gt;0,E4-D4,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="10"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46261</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>10.459999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="19" t="str">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="10"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="10"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="14"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 0 mėn. 30 d.</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="10"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46231</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="14"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46231</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="14"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46261</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="14"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="19" t="str">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="14"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="18"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="14"/>
+      <c r="N13" s="13"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="18"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="14"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3">
+        <v>10.34</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="11"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="14"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="11"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="14"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="11"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="14"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="11"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="14"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B21" s="23"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="14"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="11"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="14"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="11"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="14"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="11"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="14"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="11"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="14"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="11"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="14"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="11"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="14"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="11"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="14"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="11"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="14"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="11"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="14"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="11"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="14"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="11"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="14"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="11"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="14"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="11"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="14"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="11"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="14"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="11"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="14"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="11"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="14"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="11"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="14"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="11"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="14"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="11"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="14"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="11"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="14"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="11"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="14"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="11"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="14"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="11"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="14"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="11"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="14"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="11"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="14"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="11"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="14"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="11"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="14"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="11"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="14"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="11"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="14"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="11"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="14"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="11"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="10"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="22"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>10.34</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0.12</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="39" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="37" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="36" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355B2BCE-B3A8-4634-BB20-53D0C8F481D1}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46239</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46231</v>
+      </c>
+      <c r="F3" s="19">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v>-8</v>
+      </c>
+      <c r="G3" s="3">
+        <v>10.26</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>10.26</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0.08</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v>0.13753321766853335</v>
+      </c>
+      <c r="O3" s="6">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v>46231</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v>-8</v>
+      </c>
+      <c r="T3" s="13"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46209</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-10.26</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="19" t="str">
+        <f>IF(E4&gt;0,E4-D4,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="10"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46231</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>10.34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="19" t="str">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="10"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="10"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="14"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 0 mėn. 30 d.</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="10"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46209</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="14"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46209</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="14"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46239</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="14"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="19" t="str">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="14"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="18"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="14"/>
+      <c r="N13" s="13"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="18"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="14"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3">
+        <v>10.26</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="11"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="14"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="11"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="14"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="11"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="14"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="11"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="14"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B21" s="23"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="14"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="11"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="14"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="11"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="14"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="11"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="14"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="11"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="14"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="11"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="14"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="11"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="14"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="11"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="14"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="11"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="14"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="11"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="14"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="11"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="14"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="11"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="14"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="11"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="14"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="11"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="14"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="11"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="14"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="11"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="14"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="11"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="14"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="11"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="14"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="11"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="14"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="11"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="14"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="11"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="14"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="11"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="14"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="11"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="14"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="11"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="14"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="11"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="14"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="11"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="14"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="11"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="14"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="11"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="14"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="11"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="14"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="11"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="14"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="11"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="14"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="11"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="10"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="22"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>10.26</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0.08</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -7983,10 +11973,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355B2BCE-B3A8-4634-BB20-53D0C8F481D1}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DFB9D0-FFDA-4CA0-9F51-BFCBF06C03C2}">
   <sheetPr>
-    <tabColor rgb="FF92D050"/>
+    <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8011,31 +12001,31 @@
         <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -8102,65 +12092,57 @@
         <v>36</v>
       </c>
       <c r="D3" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E3" s="6">
-        <v>46231</v>
-      </c>
-      <c r="F3" s="19">
+        <v>46238</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="19" t="str">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v>-8</v>
-      </c>
-      <c r="G3" s="3">
-        <v>10.26</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.08</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
+        <v/>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
       <c r="J3" s="14"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>10.26</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
         <v>0</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.13753321766853335</v>
-      </c>
-      <c r="O3" s="6">
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>46231</v>
-      </c>
-      <c r="P3" s="2" t="str">
+        <v/>
+      </c>
+      <c r="P3" s="2">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="2" t="str">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>-8</v>
+        <v/>
       </c>
       <c r="T3" s="13"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-10.26</v>
+        <v>-10.24</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -8182,11 +12164,11 @@
       <c r="J4" s="10"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>46231</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>10.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -8287,7 +12269,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="6"/>
@@ -8313,7 +12295,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="6">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="6"/>
@@ -8339,7 +12321,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="6">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="6"/>
@@ -8364,9 +12346,9 @@
       <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="19" t="str">
+      <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v/>
+        <v>-27</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="6"/>
@@ -8470,7 +12452,7 @@
         <v>40</v>
       </c>
       <c r="B16" s="3">
-        <v>10.26</v>
+        <v>10.24</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="6"/>
@@ -9227,11 +13209,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>10.26</v>
+        <v>0</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -9269,8 +13251,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DFB9D0-FFDA-4CA0-9F51-BFCBF06C03C2}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E38648-85FB-451A-8C48-F23050BE99C9}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9294,31 +13279,31 @@
         <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -9385,57 +13370,65 @@
         <v>36</v>
       </c>
       <c r="D3" s="11">
-        <v>46238</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="19" t="str">
+        <v>46215</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46209</v>
+      </c>
+      <c r="F3" s="19">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>-6</v>
+      </c>
+      <c r="G3" s="3">
+        <v>10.17</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
       <c r="J3" s="14"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>0</v>
+        <v>10.17</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
         <v>0</v>
       </c>
-      <c r="N3" s="7" t="str">
+      <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="str">
+        <v>0.14338709712028502</v>
+      </c>
+      <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v/>
-      </c>
-      <c r="P3" s="2">
+        <v>46209</v>
+      </c>
+      <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v>6</v>
-      </c>
-      <c r="Q3" s="2" t="str">
+        <v/>
+      </c>
+      <c r="Q3" s="2">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v/>
+        <v>-6</v>
       </c>
       <c r="T3" s="13"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>46208</v>
+        <v>46185</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-10.24</v>
+        <v>-10.17</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -9457,11 +13450,11 @@
       <c r="J4" s="10"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>0</v>
+        <v>46209</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>0</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -9536,7 +13529,7 @@
       </c>
       <c r="B8" s="6" t="str">
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 0 mėn. 30 d.</v>
+        <v>0 m. 1 mėn. 0 d.</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="6"/>
@@ -9562,7 +13555,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>46208</v>
+        <v>46185</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="6"/>
@@ -9588,7 +13581,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="6">
-        <v>46208</v>
+        <v>46185</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="6"/>
@@ -9614,7 +13607,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="6">
-        <v>46238</v>
+        <v>46215</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="6"/>
@@ -9639,9 +13632,9 @@
       <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="19" t="str">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>-6</v>
+        <v/>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="6"/>
@@ -9745,7 +13738,7 @@
         <v>40</v>
       </c>
       <c r="B16" s="3">
-        <v>10.24</v>
+        <v>10.17</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="6"/>
@@ -10502,11 +14495,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>0</v>
+        <v>10.17</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -10544,8 +14537,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E38648-85FB-451A-8C48-F23050BE99C9}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFD3710-89A2-4F7D-A324-B3CED3BB72D8}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
@@ -10572,31 +14565,31 @@
         <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -10663,20 +14656,20 @@
         <v>36</v>
       </c>
       <c r="D3" s="11">
-        <v>46215</v>
+        <v>46208</v>
       </c>
       <c r="E3" s="6">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="F3" s="19">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3">
-        <v>10.17</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="H3" s="3">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="I3" s="3">
         <v>0</v>
@@ -10684,11 +14677,11 @@
       <c r="J3" s="14"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>10.17</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -10696,11 +14689,11 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.14338709712028502</v>
+        <v>0.14042803645133972</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
@@ -10708,16 +14701,16 @@
       </c>
       <c r="Q3" s="2">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="T3" s="13"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>46185</v>
+        <v>46178</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-10.17</v>
+        <v>-10.130000000000001</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -10743,11 +14736,11 @@
       <c r="J4" s="10"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>10.26</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -10848,7 +14841,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>46185</v>
+        <v>46178</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="6"/>
@@ -10874,7 +14867,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="6">
-        <v>46185</v>
+        <v>46178</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="6"/>
@@ -10900,7 +14893,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="6">
-        <v>46215</v>
+        <v>46208</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="6"/>
@@ -11031,7 +15024,7 @@
         <v>40</v>
       </c>
       <c r="B16" s="3">
-        <v>10.17</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="6"/>
@@ -11788,11 +15781,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>10.17</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -11830,8 +15823,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFD3710-89A2-4F7D-A324-B3CED3BB72D8}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{894C5DD5-26F0-4BD8-A02A-9EA73D3EF2C5}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
@@ -11858,31 +15851,31 @@
         <v>17</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="35"/>
+      <c r="I1" s="36"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -11949,20 +15942,20 @@
         <v>36</v>
       </c>
       <c r="D3" s="11">
-        <v>46208</v>
+        <v>46155</v>
       </c>
       <c r="E3" s="6">
-        <v>46208</v>
+        <v>46185</v>
       </c>
       <c r="F3" s="19">
         <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3" s="3">
-        <v>10.130000000000001</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="H3" s="3">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I3" s="3">
         <v>0</v>
@@ -11970,11 +15963,11 @@
       <c r="J3" s="14"/>
       <c r="K3" s="3">
         <f>G53</f>
-        <v>10.130000000000001</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -11982,11 +15975,11 @@
       </c>
       <c r="N3" s="7">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.14042803645133972</v>
+        <v>0.14999164938926698</v>
       </c>
       <c r="O3" s="6">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>46208</v>
+        <v>46185</v>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
@@ -11994,16 +15987,16 @@
       </c>
       <c r="Q3" s="2">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T3" s="13"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>46178</v>
+        <v>46154</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>-10.130000000000001</v>
+        <v>-10.050000000000001</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -12029,11 +16022,11 @@
       <c r="J4" s="10"/>
       <c r="X4" s="6">
         <f>E3</f>
-        <v>46208</v>
+        <v>46185</v>
       </c>
       <c r="Y4" s="3">
         <f>G3+H3-I3</f>
-        <v>10.24</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -12108,7 +16101,7 @@
       </c>
       <c r="B8" s="6" t="str">
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 1 mėn. 0 d.</v>
+        <v>0 m. 0 mėn. 1 d.</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="6"/>
@@ -12134,7 +16127,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6">
-        <v>46178</v>
+        <v>46154</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="6"/>
@@ -12160,7 +16153,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="6">
-        <v>46178</v>
+        <v>46124</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="6"/>
@@ -12186,7 +16179,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="6">
-        <v>46208</v>
+        <v>46155</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="6"/>
@@ -12317,7 +16310,7 @@
         <v>40</v>
       </c>
       <c r="B16" s="3">
-        <v>10.130000000000001</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="6"/>
@@ -13074,11 +17067,11 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3">
         <f>SUM(G3:G52)</f>
-        <v>10.130000000000001</v>
+        <v>10.050000000000001</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -13114,2576 +17107,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{894C5DD5-26F0-4BD8-A02A-9EA73D3EF2C5}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:Z53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="23" width="8.7109375" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="10"/>
-      <c r="K2" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="X2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z2" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="11">
-        <v>46155</v>
-      </c>
-      <c r="E3" s="6">
-        <v>46185</v>
-      </c>
-      <c r="F3" s="19">
-        <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v>30</v>
-      </c>
-      <c r="G3" s="3">
-        <v>10.050000000000001</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.12</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="3">
-        <f>G53</f>
-        <v>10.050000000000001</v>
-      </c>
-      <c r="L3" s="3">
-        <f>H53</f>
-        <v>0.12</v>
-      </c>
-      <c r="M3" s="3">
-        <f>I53</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.14999164938926698</v>
-      </c>
-      <c r="O3" s="6">
-        <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>46185</v>
-      </c>
-      <c r="P3" s="2" t="str">
-        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2">
-        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>30</v>
-      </c>
-      <c r="T3" s="13"/>
-      <c r="X3" s="6">
-        <f>B9</f>
-        <v>46154</v>
-      </c>
-      <c r="Y3" s="3">
-        <f>B16*-1</f>
-        <v>-10.050000000000001</v>
-      </c>
-      <c r="Z3" s="2" t="str">
-        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="19" t="str">
-        <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="10"/>
-      <c r="X4" s="6">
-        <f>E3</f>
-        <v>46185</v>
-      </c>
-      <c r="Y4" s="3">
-        <f>G3+H3-I3</f>
-        <v>10.17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="19" t="str">
-        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="10"/>
-      <c r="X5" s="6">
-        <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
-      </c>
-      <c r="Y5" s="3">
-        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="10"/>
-      <c r="X6" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="14"/>
-      <c r="X7" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="6" t="str">
-        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 0 mėn. 1 d.</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="10"/>
-      <c r="X8" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46154</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="14"/>
-      <c r="X9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46124</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="14"/>
-      <c r="X10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46155</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="14"/>
-      <c r="X11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="19" t="str">
-        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="14"/>
-      <c r="X12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="18"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="14"/>
-      <c r="N13" s="13"/>
-      <c r="X13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="18"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="14"/>
-      <c r="X14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0.13600000000000001</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="X15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="3">
-        <v>10.050000000000001</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="X16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="11"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="14"/>
-      <c r="X17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="11"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="14"/>
-      <c r="X18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="11"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="14"/>
-      <c r="X19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="11"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="14"/>
-      <c r="X20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B21" s="23"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="14"/>
-      <c r="X21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D22" s="11"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="14"/>
-      <c r="X22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D23" s="11"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="14"/>
-      <c r="X23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D24" s="11"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="14"/>
-      <c r="X24" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D25" s="11"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="14"/>
-      <c r="X25" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D26" s="11"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="14"/>
-      <c r="X26" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D27" s="11"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="14"/>
-      <c r="X27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D28" s="11"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="14"/>
-      <c r="X28" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D29" s="11"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="14"/>
-      <c r="X29" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D30" s="11"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="14"/>
-      <c r="X30" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D31" s="11"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="14"/>
-      <c r="X31" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D32" s="11"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="14"/>
-      <c r="X32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D33" s="11"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="14"/>
-      <c r="X33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D34" s="11"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="14"/>
-      <c r="X34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D35" s="11"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="14"/>
-      <c r="X35" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D36" s="11"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="14"/>
-      <c r="X36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D37" s="11"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="14"/>
-      <c r="X37" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D38" s="11"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="14"/>
-      <c r="X38" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D39" s="11"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="14"/>
-      <c r="X39" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D40" s="11"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="14"/>
-      <c r="X40" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D41" s="11"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="14"/>
-      <c r="X41" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D42" s="11"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="14"/>
-      <c r="X42" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D43" s="11"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="14"/>
-      <c r="X43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D44" s="11"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="14"/>
-      <c r="X44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D45" s="11"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="14"/>
-      <c r="X45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D46" s="11"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="14"/>
-      <c r="X46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D47" s="11"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="14"/>
-      <c r="X47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D48" s="11"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="14"/>
-      <c r="X48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D49" s="11"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="14"/>
-      <c r="X49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D50" s="11"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="14"/>
-      <c r="X50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D51" s="11"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="14"/>
-      <c r="X51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D52" s="11"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="10"/>
-      <c r="X52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D53" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" s="22"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <f>SUM(G3:G52)</f>
-        <v>10.050000000000001</v>
-      </c>
-      <c r="H53" s="3">
-        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.12</v>
-      </c>
-      <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="X1:Z1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="15" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2">
-      <formula>$B$16=$K$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="13" priority="3">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="12" priority="4">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D73BEB5-FF23-4AB2-910E-BFC1E1552858}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:Z53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="23" width="8.7109375" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
-    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
-    <col min="26" max="26" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="10"/>
-      <c r="K2" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="X2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z2" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="11">
-        <v>46181</v>
-      </c>
-      <c r="E3" s="6">
-        <v>46177</v>
-      </c>
-      <c r="F3" s="19">
-        <f>IF(E3&gt;0,E3-D3,"")</f>
-        <v>-4</v>
-      </c>
-      <c r="G3" s="3">
-        <v>10.029999999999999</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="3">
-        <f>G53</f>
-        <v>10.029999999999999</v>
-      </c>
-      <c r="L3" s="3">
-        <f>H53</f>
-        <v>0.1</v>
-      </c>
-      <c r="M3" s="3">
-        <f>I53</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>0.1435224711894989</v>
-      </c>
-      <c r="O3" s="6">
-        <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>46177</v>
-      </c>
-      <c r="P3" s="2" t="str">
-        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="2">
-        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>-4</v>
-      </c>
-      <c r="T3" s="13"/>
-      <c r="X3" s="6">
-        <f>B9</f>
-        <v>46150</v>
-      </c>
-      <c r="Y3" s="3">
-        <f>B16*-1</f>
-        <v>-10.029999999999999</v>
-      </c>
-      <c r="Z3" s="2" t="str">
-        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="19" t="str">
-        <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="10"/>
-      <c r="X4" s="6">
-        <f>E3</f>
-        <v>46177</v>
-      </c>
-      <c r="Y4" s="3">
-        <f>G3+H3-I3</f>
-        <v>10.129999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="19" t="str">
-        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="10"/>
-      <c r="X5" s="6">
-        <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
-      </c>
-      <c r="Y5" s="3">
-        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="10"/>
-      <c r="X6" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="14"/>
-      <c r="X7" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="6" t="str">
-        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 1 mėn. 0 d.</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="10"/>
-      <c r="X8" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="14"/>
-      <c r="X9" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46150</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="14"/>
-      <c r="X10" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46181</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="14"/>
-      <c r="X11" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="19" t="str">
-        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="14"/>
-      <c r="X12" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="18"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="14"/>
-      <c r="N13" s="13"/>
-      <c r="X13" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="18"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="14"/>
-      <c r="X14" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0.13600000000000001</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="X15" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="3">
-        <v>10.029999999999999</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="X16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D17" s="11"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="14"/>
-      <c r="X17" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D18" s="11"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="14"/>
-      <c r="X18" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D19" s="11"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="14"/>
-      <c r="X19" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D20" s="11"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="14"/>
-      <c r="X20" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B21" s="23"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="14"/>
-      <c r="X21" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D22" s="11"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="14"/>
-      <c r="X22" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D23" s="11"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="14"/>
-      <c r="X23" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D24" s="11"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="14"/>
-      <c r="X24" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D25" s="11"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="14"/>
-      <c r="X25" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D26" s="11"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="14"/>
-      <c r="X26" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D27" s="11"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="14"/>
-      <c r="X27" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D28" s="11"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="14"/>
-      <c r="X28" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D29" s="11"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="14"/>
-      <c r="X29" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D30" s="11"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="14"/>
-      <c r="X30" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D31" s="11"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="14"/>
-      <c r="X31" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="D32" s="11"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="14"/>
-      <c r="X32" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D33" s="11"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="14"/>
-      <c r="X33" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D34" s="11"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="14"/>
-      <c r="X34" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D35" s="11"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="14"/>
-      <c r="X35" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D36" s="11"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="14"/>
-      <c r="X36" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D37" s="11"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="14"/>
-      <c r="X37" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D38" s="11"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="14"/>
-      <c r="X38" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D39" s="11"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="14"/>
-      <c r="X39" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y39" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D40" s="11"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="14"/>
-      <c r="X40" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y40" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D41" s="11"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="14"/>
-      <c r="X41" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D42" s="11"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="14"/>
-      <c r="X42" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D43" s="11"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="14"/>
-      <c r="X43" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y43" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D44" s="11"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="14"/>
-      <c r="X44" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D45" s="11"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="14"/>
-      <c r="X45" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D46" s="11"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="14"/>
-      <c r="X46" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D47" s="11"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="14"/>
-      <c r="X47" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D48" s="11"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="14"/>
-      <c r="X48" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D49" s="11"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="14"/>
-      <c r="X49" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D50" s="11"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="14"/>
-      <c r="X50" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y50" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D51" s="11"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="14"/>
-      <c r="X51" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D52" s="11"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="10"/>
-      <c r="X52" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
-      <c r="D53" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" s="22"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <f>SUM(G3:G52)</f>
-        <v>10.029999999999999</v>
-      </c>
-      <c r="H53" s="3">
-        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.1</v>
-      </c>
-      <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="X1:Z1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="11" priority="1">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
-      <formula>$B$16=$K$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="expression" dxfId="9" priority="3">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z3">
-    <cfRule type="expression" dxfId="8" priority="4">
-      <formula>$Z$3="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>